--- a/final_data_pipeline/output/311224longform_elec_options_nowhp.xlsx
+++ b/final_data_pipeline/output/311224longform_elec_options_nowhp.xlsx
@@ -708,7 +708,7 @@
         <v>83</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="J2">
         <v>8000</v>
@@ -723,10 +723,10 @@
         <v>1290639.050312052</v>
       </c>
       <c r="N2">
-        <v>1.741590909090909</v>
+        <v>1.815485677363773</v>
       </c>
       <c r="O2">
-        <v>1.89075</v>
+        <v>1.979371877230549</v>
       </c>
       <c r="P2">
         <v>161.3298812890064</v>
@@ -761,7 +761,7 @@
         <v>83</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="J3">
         <v>8000</v>
@@ -776,10 +776,10 @@
         <v>1699222.622824276</v>
       </c>
       <c r="N3">
-        <v>1.741590909090909</v>
+        <v>1.620655622136059</v>
       </c>
       <c r="O3">
-        <v>1.89075</v>
+        <v>1.747323835194455</v>
       </c>
       <c r="P3">
         <v>212.4028278530345</v>
@@ -867,7 +867,7 @@
         <v>83</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="J5">
         <v>8000</v>
@@ -882,10 +882,10 @@
         <v>353355.3409251557</v>
       </c>
       <c r="N5">
-        <v>1.741590909090909</v>
+        <v>1.815485677363773</v>
       </c>
       <c r="O5">
-        <v>1.89075</v>
+        <v>1.979371877230549</v>
       </c>
       <c r="P5">
         <v>44.16941761564447</v>
@@ -973,7 +973,7 @@
         <v>83</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="J7">
         <v>8000</v>
@@ -988,10 +988,10 @@
         <v>981773.3387304785</v>
       </c>
       <c r="N7">
-        <v>1.741590909090909</v>
+        <v>1.815485677363773</v>
       </c>
       <c r="O7">
-        <v>1.89075</v>
+        <v>1.979371877230549</v>
       </c>
       <c r="P7">
         <v>122.7216673413098</v>
@@ -1026,7 +1026,7 @@
         <v>83</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="J8">
         <v>8000</v>
@@ -1041,10 +1041,10 @@
         <v>419439.6624431778</v>
       </c>
       <c r="N8">
-        <v>1.741590909090909</v>
+        <v>1.815485677363773</v>
       </c>
       <c r="O8">
-        <v>1.89075</v>
+        <v>1.979371877230549</v>
       </c>
       <c r="P8">
         <v>52.42995780539723</v>
@@ -1079,7 +1079,7 @@
         <v>83</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="J9">
         <v>8000</v>
@@ -1094,10 +1094,10 @@
         <v>1076997.406245252</v>
       </c>
       <c r="N9">
-        <v>1.741590909090909</v>
+        <v>1.803394296576035</v>
       </c>
       <c r="O9">
-        <v>1.89075</v>
+        <v>1.964819060413116</v>
       </c>
       <c r="P9">
         <v>134.6246757806565</v>
@@ -1185,7 +1185,7 @@
         <v>83</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="J11">
         <v>8000</v>
@@ -1200,10 +1200,10 @@
         <v>445451.2421278559</v>
       </c>
       <c r="N11">
-        <v>1.741590909090909</v>
+        <v>1.620655622136059</v>
       </c>
       <c r="O11">
-        <v>1.89075</v>
+        <v>1.747323835194455</v>
       </c>
       <c r="P11">
         <v>55.68140526598199</v>
@@ -1338,7 +1338,7 @@
         <v>83</v>
       </c>
       <c r="I14">
-        <v>10</v>
+        <v>16.97685185185183</v>
       </c>
       <c r="J14">
         <v>8000</v>
@@ -1353,10 +1353,10 @@
         <v>466423.2930743959</v>
       </c>
       <c r="N14">
-        <v>1.741590909090909</v>
+        <v>1.859533546038736</v>
       </c>
       <c r="O14">
-        <v>1.89075</v>
+        <v>2.032558602498382</v>
       </c>
       <c r="P14">
         <v>58.30291163429948</v>
@@ -1391,7 +1391,7 @@
         <v>83</v>
       </c>
       <c r="I15">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="J15">
         <v>8000</v>
@@ -1406,10 +1406,10 @@
         <v>678092.7995180225</v>
       </c>
       <c r="N15">
-        <v>1.741590909090909</v>
+        <v>1.546865537736907</v>
       </c>
       <c r="O15">
-        <v>1.89075</v>
+        <v>1.660778333536659</v>
       </c>
       <c r="P15">
         <v>84.76159993975281</v>
@@ -1550,7 +1550,7 @@
         <v>83</v>
       </c>
       <c r="I18">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="J18">
         <v>8000</v>
@@ -1565,10 +1565,10 @@
         <v>536365.7758239276</v>
       </c>
       <c r="N18">
-        <v>1.741590909090909</v>
+        <v>1.815485677363773</v>
       </c>
       <c r="O18">
-        <v>1.89075</v>
+        <v>1.979371877230549</v>
       </c>
       <c r="P18">
         <v>67.04572197799095</v>
@@ -1603,7 +1603,7 @@
         <v>83</v>
       </c>
       <c r="I19">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="J19">
         <v>8000</v>
@@ -1618,10 +1618,10 @@
         <v>917813.4031196755</v>
       </c>
       <c r="N19">
-        <v>1.741590909090909</v>
+        <v>1.672603071948262</v>
       </c>
       <c r="O19">
-        <v>1.89075</v>
+        <v>1.808689105403011</v>
       </c>
       <c r="P19">
         <v>114.7266753899594</v>
@@ -1709,7 +1709,7 @@
         <v>83</v>
       </c>
       <c r="I21">
-        <v>10</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="J21">
         <v>8000</v>
@@ -1724,10 +1724,10 @@
         <v>429860.7724820906</v>
       </c>
       <c r="N21">
-        <v>1.741590909090909</v>
+        <v>1.600162412993039</v>
       </c>
       <c r="O21">
-        <v>1.89075</v>
+        <v>1.723215189873418</v>
       </c>
       <c r="P21">
         <v>53.73259656026133</v>
@@ -1762,7 +1762,7 @@
         <v>83</v>
       </c>
       <c r="I22">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="J22">
         <v>8000</v>
@@ -1777,10 +1777,10 @@
         <v>942642.7811614531</v>
       </c>
       <c r="N22">
-        <v>1.741590909090909</v>
+        <v>1.620655622136059</v>
       </c>
       <c r="O22">
-        <v>1.89075</v>
+        <v>1.747323835194455</v>
       </c>
       <c r="P22">
         <v>117.8303476451816</v>
@@ -1815,7 +1815,7 @@
         <v>83</v>
       </c>
       <c r="I23">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="J23">
         <v>8000</v>
@@ -1830,10 +1830,10 @@
         <v>491251.1649361285</v>
       </c>
       <c r="N23">
-        <v>1.741590909090909</v>
+        <v>1.798225615362447</v>
       </c>
       <c r="O23">
-        <v>1.89075</v>
+        <v>1.958604378795604</v>
       </c>
       <c r="P23">
         <v>61.40639561701607</v>
@@ -1868,7 +1868,7 @@
         <v>83</v>
       </c>
       <c r="I24">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="J24">
         <v>8000</v>
@@ -1883,10 +1883,10 @@
         <v>1247352.041344643</v>
       </c>
       <c r="N24">
-        <v>1.741590909090909</v>
+        <v>1.911855479578636</v>
       </c>
       <c r="O24">
-        <v>1.89075</v>
+        <v>2.09608909874769</v>
       </c>
       <c r="P24">
         <v>155.9190051680804</v>
@@ -2080,7 +2080,7 @@
         <v>83</v>
       </c>
       <c r="I28">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="J28">
         <v>8000</v>
@@ -2095,10 +2095,10 @@
         <v>384834.4080788534</v>
       </c>
       <c r="N28">
-        <v>1.741590909090909</v>
+        <v>1.940636870984383</v>
       </c>
       <c r="O28">
-        <v>1.89075</v>
+        <v>2.131200751448103</v>
       </c>
       <c r="P28">
         <v>48.10430100985668</v>
@@ -2133,7 +2133,7 @@
         <v>83</v>
       </c>
       <c r="I29">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="J29">
         <v>8000</v>
@@ -2148,10 +2148,10 @@
         <v>763843.0858607751</v>
       </c>
       <c r="N29">
-        <v>1.741590909090909</v>
+        <v>1.620655622136059</v>
       </c>
       <c r="O29">
-        <v>1.89075</v>
+        <v>1.747323835194455</v>
       </c>
       <c r="P29">
         <v>95.48038573259689</v>
@@ -2239,7 +2239,7 @@
         <v>85</v>
       </c>
       <c r="I31">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="J31">
         <v>8000</v>
@@ -2286,7 +2286,7 @@
         <v>83</v>
       </c>
       <c r="I32">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="J32">
         <v>8000</v>
@@ -2301,10 +2301,10 @@
         <v>1253385.688345612</v>
       </c>
       <c r="N32">
-        <v>1.741590909090909</v>
+        <v>1.784922174701128</v>
       </c>
       <c r="O32">
-        <v>1.89075</v>
+        <v>1.942625691911729</v>
       </c>
       <c r="P32">
         <v>156.6732110432015</v>
@@ -2339,7 +2339,7 @@
         <v>83</v>
       </c>
       <c r="I33">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="J33">
         <v>8000</v>
@@ -2354,10 +2354,10 @@
         <v>345779.7776501709</v>
       </c>
       <c r="N33">
-        <v>1.741590909090909</v>
+        <v>1.909121107266436</v>
       </c>
       <c r="O33">
-        <v>1.89075</v>
+        <v>2.092759415833974</v>
       </c>
       <c r="P33">
         <v>43.22247220627136</v>
@@ -2392,7 +2392,7 @@
         <v>83</v>
       </c>
       <c r="I34">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="J34">
         <v>8000</v>
@@ -2407,10 +2407,10 @@
         <v>963519.942765158</v>
       </c>
       <c r="N34">
-        <v>1.741590909090909</v>
+        <v>1.940636870984383</v>
       </c>
       <c r="O34">
-        <v>1.89075</v>
+        <v>2.131200751448103</v>
       </c>
       <c r="P34">
         <v>120.4399928456448</v>
@@ -2445,7 +2445,7 @@
         <v>85</v>
       </c>
       <c r="I35">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="J35">
         <v>8000</v>
@@ -2492,7 +2492,7 @@
         <v>83</v>
       </c>
       <c r="I36">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="J36">
         <v>8000</v>
@@ -2507,10 +2507,10 @@
         <v>681992.29965452</v>
       </c>
       <c r="N36">
-        <v>1.741590909090909</v>
+        <v>1.790685487585954</v>
       </c>
       <c r="O36">
-        <v>1.89075</v>
+        <v>1.94954496878686</v>
       </c>
       <c r="P36">
         <v>85.249037456815</v>
@@ -2545,7 +2545,7 @@
         <v>83</v>
       </c>
       <c r="I37">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="J37">
         <v>8000</v>
@@ -2560,10 +2560,10 @@
         <v>1168309.054993405</v>
       </c>
       <c r="N37">
-        <v>1.741590909090909</v>
+        <v>1.908284719500103</v>
       </c>
       <c r="O37">
-        <v>1.89075</v>
+        <v>2.091741145739967</v>
       </c>
       <c r="P37">
         <v>146.0386318741756</v>
@@ -2651,7 +2651,7 @@
         <v>83</v>
       </c>
       <c r="I39">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="J39">
         <v>8000</v>
@@ -2666,10 +2666,10 @@
         <v>1062080.940457618</v>
       </c>
       <c r="N39">
-        <v>1.741590909090909</v>
+        <v>1.815485677363773</v>
       </c>
       <c r="O39">
-        <v>1.89075</v>
+        <v>1.979371877230549</v>
       </c>
       <c r="P39">
         <v>132.7601175572023</v>
@@ -2704,7 +2704,7 @@
         <v>83</v>
       </c>
       <c r="I40">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="J40">
         <v>8000</v>
@@ -2719,10 +2719,10 @@
         <v>912490.5628406557</v>
       </c>
       <c r="N40">
-        <v>1.741590909090909</v>
+        <v>1.815485677363773</v>
       </c>
       <c r="O40">
-        <v>1.89075</v>
+        <v>1.979371877230549</v>
       </c>
       <c r="P40">
         <v>114.061320355082</v>
@@ -2757,7 +2757,7 @@
         <v>83</v>
       </c>
       <c r="I41">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="J41">
         <v>8000</v>
@@ -2772,10 +2772,10 @@
         <v>816241.1394252041</v>
       </c>
       <c r="N41">
-        <v>1.741590909090909</v>
+        <v>1.8239809580482</v>
       </c>
       <c r="O41">
-        <v>1.89075</v>
+        <v>1.989608681354817</v>
       </c>
       <c r="P41">
         <v>102.0301424281505</v>
@@ -2810,7 +2810,7 @@
         <v>85</v>
       </c>
       <c r="I42">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="J42">
         <v>8000</v>
@@ -2857,7 +2857,7 @@
         <v>83</v>
       </c>
       <c r="I43">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="J43">
         <v>8000</v>
@@ -2872,10 +2872,10 @@
         <v>725609.7675775918</v>
       </c>
       <c r="N43">
-        <v>1.741590909090909</v>
+        <v>1.798225615362447</v>
       </c>
       <c r="O43">
-        <v>1.89075</v>
+        <v>1.958604378795604</v>
       </c>
       <c r="P43">
         <v>90.70122094719898</v>
@@ -2963,7 +2963,7 @@
         <v>83</v>
       </c>
       <c r="I45">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="J45">
         <v>8000</v>
@@ -2978,10 +2978,10 @@
         <v>1691584.783816095</v>
       </c>
       <c r="N45">
-        <v>1.741590909090909</v>
+        <v>1.815485677363773</v>
       </c>
       <c r="O45">
-        <v>1.89075</v>
+        <v>1.979371877230549</v>
       </c>
       <c r="P45">
         <v>211.4480979770119</v>
@@ -3069,7 +3069,7 @@
         <v>83</v>
       </c>
       <c r="I47">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="J47">
         <v>8000</v>
@@ -3084,10 +3084,10 @@
         <v>813915.3130593229</v>
       </c>
       <c r="N47">
-        <v>1.741590909090909</v>
+        <v>1.803394296576035</v>
       </c>
       <c r="O47">
-        <v>1.89075</v>
+        <v>1.964819060413116</v>
       </c>
       <c r="P47">
         <v>101.7394141324154</v>
@@ -3281,7 +3281,7 @@
         <v>83</v>
       </c>
       <c r="I51">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="J51">
         <v>8000</v>
@@ -3296,10 +3296,10 @@
         <v>940461.8606503607</v>
       </c>
       <c r="N51">
-        <v>1.741590909090909</v>
+        <v>1.790685487585954</v>
       </c>
       <c r="O51">
-        <v>1.89075</v>
+        <v>1.94954496878686</v>
       </c>
       <c r="P51">
         <v>117.5577325812951</v>
@@ -3334,7 +3334,7 @@
         <v>83</v>
       </c>
       <c r="I52">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="J52">
         <v>8000</v>
@@ -3349,10 +3349,10 @@
         <v>457457.2891348442</v>
       </c>
       <c r="N52">
-        <v>1.741590909090909</v>
+        <v>1.803394296576035</v>
       </c>
       <c r="O52">
-        <v>1.89075</v>
+        <v>1.964819060413116</v>
       </c>
       <c r="P52">
         <v>57.18216114185552</v>
@@ -3593,7 +3593,7 @@
         <v>83</v>
       </c>
       <c r="I57">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="J57">
         <v>8000</v>
@@ -3608,10 +3608,10 @@
         <v>549582.5057187775</v>
       </c>
       <c r="N57">
-        <v>1.741590909090909</v>
+        <v>1.672603071948262</v>
       </c>
       <c r="O57">
-        <v>1.89075</v>
+        <v>1.808689105403011</v>
       </c>
       <c r="P57">
         <v>68.69781321484719</v>
